--- a/data/trans_camb/IP19C08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 16,77</t>
+          <t>-9,19; 15,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 1,83</t>
+          <t>-15,45; 2,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 9,03</t>
+          <t>-11,5; 8,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,4; -1,48</t>
+          <t>-26,23; -1,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 0,4</t>
+          <t>-23,74; 1,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 6,48</t>
+          <t>-20,97; 7,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 3,41</t>
+          <t>-14,25; 2,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -1,02</t>
+          <t>-16,8; -0,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 4,75</t>
+          <t>-14,06; 3,96</t>
         </is>
       </c>
     </row>
@@ -798,39 +798,39 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,55</t>
+          <t>-100,0; 196,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 81,47</t>
+          <t>-100,0; 120,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,15</t>
+          <t>-92,36; 239,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,68; 94,28</t>
+          <t>-88,1; 124,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 11,24</t>
+          <t>-100,0; 39,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-84,89; 115,89</t>
+          <t>-82,25; 103,78</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 2,59</t>
+          <t>-7,64; 1,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 8,51</t>
+          <t>-3,19; 9,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -1,06</t>
+          <t>-9,02; -1,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,7</t>
+          <t>-2,07; 5,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 7,22</t>
+          <t>-1,93; 6,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,0</t>
+          <t>-5,19; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,65</t>
+          <t>-3,1; 2,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 5,95</t>
+          <t>-1,59; 5,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; -0,54</t>
+          <t>-5,33; -0,54</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,42; 837,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 362,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 1133,15</t>
+          <t>-57,64; 687,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 6,12</t>
+          <t>-10,03; 6,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -1,95</t>
+          <t>-14,13; -1,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -1,95</t>
+          <t>-14,2; -1,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 7,43</t>
+          <t>-14,13; 7,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,19; -3,61</t>
+          <t>-21,4; -5,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -2,5</t>
+          <t>-20,2; -2,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 3,74</t>
+          <t>-10,07; 4,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,17; -3,84</t>
+          <t>-15,04; -3,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,54; -3,64</t>
+          <t>-14,18; -3,12</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-87,5; 168,94</t>
+          <t>-85,81; 203,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-80,66; 86,22</t>
+          <t>-81,54; 116,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -40,6</t>
+          <t>-100,0; -37,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 6,22</t>
+          <t>-15,39; 6,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 4,32</t>
+          <t>-15,64; 4,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -3,94</t>
+          <t>-20,93; -4,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 7,69</t>
+          <t>-6,02; 6,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 8,85</t>
+          <t>-3,96; 8,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 14,36</t>
+          <t>-2,5; 13,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 4,09</t>
+          <t>-7,46; 4,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 4,08</t>
+          <t>-8,62; 3,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 3,19</t>
+          <t>-9,16; 2,84</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,16; 187,86</t>
+          <t>-88,82; 171,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-86,11; 123,25</t>
+          <t>-89,59; 138,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,84; 142,49</t>
+          <t>-81,12; 132,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-70,8; 151,73</t>
+          <t>-77,68; 125,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-93,49; 189,38</t>
+          <t>-100,0; 140,83</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 0,0</t>
+          <t>-20,43; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 0,0</t>
+          <t>-20,97; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 6,87</t>
+          <t>-16,07; 6,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,35</t>
+          <t>0,0; 12,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 14,44</t>
+          <t>1,67; 14,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 1,24</t>
+          <t>-11,09; 1,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 0,0</t>
+          <t>-11,45; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 6,47</t>
+          <t>-6,66; 6,99</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 8,02</t>
+          <t>-10,34; 8,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 14,16</t>
+          <t>-6,7; 13,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 4,62</t>
+          <t>-13,08; 2,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,26; 20,17</t>
+          <t>2,34; 22,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,99</t>
+          <t>0,0; 12,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,31</t>
+          <t>0,0; 19,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 10,91</t>
+          <t>-1,03; 11,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 9,48</t>
+          <t>-2,43; 8,82</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 8,15</t>
+          <t>-2,94; 7,11</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-59,59; —</t>
+          <t>-57,28; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,13; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 7,63</t>
+          <t>-7,49; 8,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 4,43</t>
+          <t>-10,68; 4,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 1,02</t>
+          <t>-11,96; 1,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 0,06</t>
+          <t>-13,34; 0,01</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 6,17</t>
+          <t>-10,63; 5,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 8,6</t>
+          <t>-11,25; 7,88</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,94</t>
+          <t>-8,52; 1,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 2,63</t>
+          <t>-7,83; 3,42</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 2,83</t>
+          <t>-9,43; 3,27</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-73,52; 174,25</t>
+          <t>-68,97; 205,9</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-85,64; 126,52</t>
+          <t>-84,28; 96,48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-90,86; 88,38</t>
+          <t>-93,18; 55,14</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-93,45; 17,83</t>
+          <t>-100,0; 22,44</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 131,81</t>
+          <t>-75,94; 116,28</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-92,13; 299,68</t>
+          <t>-91,09; 295,63</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-71,72; 38,06</t>
+          <t>-72,92; 33,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-68,46; 45,61</t>
+          <t>-68,4; 72,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-84,75; 63,93</t>
+          <t>-83,92; 74,71</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,6</t>
+          <t>-4,51; 1,63</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,48; -0,56</t>
+          <t>-6,07; -0,56</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 6,14</t>
+          <t>-2,92; 5,69</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,84</t>
+          <t>-4,45; 5,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,98; -0,81</t>
+          <t>-7,8; -0,81</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,43; -0,32</t>
+          <t>-7,02; -0,24</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,91</t>
+          <t>-3,27; 1,96</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -1,1</t>
+          <t>-5,3; -1,12</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,76</t>
+          <t>-3,53; 1,74</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 565,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-85,74; 159,58</t>
+          <t>-84,88; 163,68</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-86,48; 224,55</t>
+          <t>-88,07; 157,84</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,29</t>
+          <t>-4,28; 1,06</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,75</t>
+          <t>-4,53; 0,87</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -1,4</t>
+          <t>-6,07; -1,31</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,32</t>
+          <t>-3,75; 1,27</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,21</t>
+          <t>-4,47; 0,12</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,58</t>
+          <t>-4,01; 1,87</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,52</t>
+          <t>-3,16; 0,43</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,23</t>
+          <t>-3,82; -0,34</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,34</t>
+          <t>-4,17; -0,36</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 31,32</t>
+          <t>-59,58; 26,06</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 19,33</t>
+          <t>-62,9; 22,04</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-81,87; -28,99</t>
+          <t>-81,98; -27,66</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 41,08</t>
+          <t>-58,44; 38,3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-72,3; 10,55</t>
+          <t>-72,14; 9,23</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 49,33</t>
+          <t>-65,86; 62,66</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 13,32</t>
+          <t>-50,89; 11,28</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-59,72; -4,41</t>
+          <t>-60,35; -5,23</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-65,0; -5,12</t>
+          <t>-67,38; -7,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 15,94</t>
+          <t>-9,1; 17,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 2,09</t>
+          <t>-17,69; 1,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 8,51</t>
+          <t>-13,02; 8,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,23; -1,36</t>
+          <t>-26,64; -1,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 1,69</t>
+          <t>-23,25; 0,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 7,15</t>
+          <t>-19,79; 5,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 2,89</t>
+          <t>-14,67; 2,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,8; -0,46</t>
+          <t>-16,69; -0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 3,96</t>
+          <t>-13,77; 5,27</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 196,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,64</t>
+          <t>-100,0; 79,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,36; 239,35</t>
+          <t>-100,0; 178,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-88,1; 124,28</t>
+          <t>-91,87; 90,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,9</t>
+          <t>-100,0; 47,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-82,25; 103,78</t>
+          <t>-83,49; 129,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 1,71</t>
+          <t>-6,6; 2,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 9,25</t>
+          <t>-3,1; 9,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,02; -1,07</t>
+          <t>-9,99; -1,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,5</t>
+          <t>-1,91; 5,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 6,09</t>
+          <t>-1,05; 7,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 0,0</t>
+          <t>-5,16; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 2,44</t>
+          <t>-3,1; 2,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,49</t>
+          <t>-1,4; 5,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -0,54</t>
+          <t>-4,84; -0,52</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,42; 837,1</t>
+          <t>-73,69; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 362,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,64; 687,89</t>
+          <t>-50,98; 839,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 6,27</t>
+          <t>-9,99; 6,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -1,95</t>
+          <t>-15,75; -1,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,2; -1,95</t>
+          <t>-15,67; -1,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 7,1</t>
+          <t>-13,94; 9,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,4; -5,29</t>
+          <t>-21,29; -3,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,2; -2,56</t>
+          <t>-20,4; -2,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 4,1</t>
+          <t>-9,37; 4,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -3,74</t>
+          <t>-14,82; -3,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -3,12</t>
+          <t>-13,83; -3,51</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-85,81; 203,11</t>
+          <t>-83,16; 271,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 55,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,54; 116,91</t>
+          <t>-76,52; 93,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -37,84</t>
+          <t>-100,0; -49,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 6,19</t>
+          <t>-15,92; 5,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 4,97</t>
+          <t>-14,85; 4,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -4,9</t>
+          <t>-21,57; -4,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 6,13</t>
+          <t>-4,49; 6,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 8,33</t>
+          <t>-4,55; 8,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 13,98</t>
+          <t>-2,98; 15,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 4,16</t>
+          <t>-7,58; 4,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 3,83</t>
+          <t>-7,57; 4,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 2,84</t>
+          <t>-9,65; 3,14</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,82; 171,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,59; 138,94</t>
+          <t>-85,61; 109,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-81,12; 132,26</t>
+          <t>-79,44; 149,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,68; 125,44</t>
+          <t>-73,15; 166,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 140,83</t>
+          <t>-96,68; 179,64</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 0,0</t>
+          <t>-20,81; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 0,0</t>
+          <t>-20,93; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 6,66</t>
+          <t>-17,36; 5,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,43</t>
+          <t>0,0; 10,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 14,14</t>
+          <t>1,67; 16,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 1,83</t>
+          <t>-11,27; 1,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 0,0</t>
+          <t>-13,67; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 6,99</t>
+          <t>-6,23; 6,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 8,06</t>
+          <t>-10,5; 9,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 13,59</t>
+          <t>-6,91; 14,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 2,64</t>
+          <t>-13,34; 4,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,34; 22,23</t>
+          <t>2,19; 20,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,46</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,07</t>
+          <t>0,0; 18,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 11,43</t>
+          <t>-0,74; 11,0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 8,82</t>
+          <t>-2,53; 8,72</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 7,11</t>
+          <t>-3,53; 7,95</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-57,28; —</t>
+          <t>-62,25; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-80,13; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 8,19</t>
+          <t>-7,78; 8,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 4,13</t>
+          <t>-10,89; 4,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 1,1</t>
+          <t>-12,41; 0,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 0,01</t>
+          <t>-13,26; 0,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 5,19</t>
+          <t>-9,83; 5,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 7,88</t>
+          <t>-11,21; 8,07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 1,99</t>
+          <t>-7,63; 2,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 3,42</t>
+          <t>-7,77; 2,53</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 3,27</t>
+          <t>-9,12; 3,66</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-68,97; 205,9</t>
+          <t>-68,56; 196,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-84,28; 96,48</t>
+          <t>-84,83; 137,76</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-93,18; 55,14</t>
+          <t>-92,36; 45,36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,44</t>
+          <t>-93,99; 57,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-75,94; 116,28</t>
+          <t>-76,34; 104,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-91,09; 295,63</t>
+          <t>-93,04; 208,09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-72,92; 33,37</t>
+          <t>-70,25; 48,78</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-68,4; 72,31</t>
+          <t>-71,13; 44,54</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-83,92; 74,71</t>
+          <t>-83,79; 94,03</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,63</t>
+          <t>-4,4; 1,14</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -0,56</t>
+          <t>-5,68; -0,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,69</t>
+          <t>-2,72; 5,45</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 5,22</t>
+          <t>-4,84; 4,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -0,81</t>
+          <t>-7,89; -0,8</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,02; -0,24</t>
+          <t>-7,14; -0,08</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,96</t>
+          <t>-3,21; 2,08</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -1,12</t>
+          <t>-5,17; -0,99</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,74</t>
+          <t>-3,27; 1,77</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-84,88; 163,68</t>
+          <t>-88,03; 214,92</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-88,07; 157,84</t>
+          <t>-86,35; 202,68</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,06</t>
+          <t>-4,36; 0,95</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,87</t>
+          <t>-4,54; 0,79</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -1,31</t>
+          <t>-5,87; -1,18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,27</t>
+          <t>-3,61; 1,4</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,12</t>
+          <t>-4,63; 0,02</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,87</t>
+          <t>-3,99; 1,69</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,43</t>
+          <t>-3,17; 0,57</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -0,34</t>
+          <t>-3,81; -0,23</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,36</t>
+          <t>-4,23; -0,51</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 26,06</t>
+          <t>-60,84; 24,26</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-62,9; 22,04</t>
+          <t>-62,76; 18,43</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-81,98; -27,66</t>
+          <t>-81,15; -26,09</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 38,3</t>
+          <t>-58,58; 46,11</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 9,23</t>
+          <t>-73,75; 2,91</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 62,66</t>
+          <t>-66,02; 53,05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 11,28</t>
+          <t>-50,27; 13,74</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-60,35; -5,23</t>
+          <t>-60,15; -3,77</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-67,38; -7,5</t>
+          <t>-68,31; -6,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-11,48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-9,71</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-11,48</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-9,71</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,5</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-3,35</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 17,45</t>
+          <t>-27,4; -1,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 1,82</t>
+          <t>-24,63; 0,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 8,42</t>
+          <t>-22,47; 6,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,64; -1,91</t>
+          <t>-8,72; 16,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 0,89</t>
+          <t>-17,58; 1,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 5,83</t>
+          <t>-12,21; 10,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 2,84</t>
+          <t>-14,93; 3,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,69; -0,45</t>
+          <t>-16,75; -1,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 5,27</t>
+          <t>-12,74; 5,38</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-84,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-71,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-45,92%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>53,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-69,98%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,74%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-84,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-71,62%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-47,94%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-37,72%</t>
+          <t>-32,52%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 54,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 81,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 152,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 178,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,87; 90,12</t>
+          <t>-91,68; 94,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,85</t>
+          <t>-100,0; 11,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,49; 129,8</t>
+          <t>-82,97; 127,93</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,03</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,44</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-3,34</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 2,78</t>
+          <t>-1,05; 5,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 9,31</t>
+          <t>-2,0; 7,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -1,09</t>
+          <t>-5,89; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,44</t>
+          <t>-6,69; 2,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,14</t>
+          <t>-4,32; 8,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,0</t>
+          <t>-10,03; -1,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 2,61</t>
+          <t>-3,13; 2,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,79</t>
+          <t>-1,37; 5,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; -0,52</t>
+          <t>-5,29; -0,54</t>
         </is>
       </c>
     </row>
@@ -946,27 +946,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>111,32%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>130,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-60,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>73,08%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>111,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>130,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,69; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,98; 839,32</t>
+          <t>-50,04; 1133,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,37</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-10,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-9,73</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,96</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,93</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-5,93</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,37</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-10,69</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-9,64</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-2,56</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,76</t>
+          <t>-7,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 6,13</t>
+          <t>-12,51; 7,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,75; -1,95</t>
+          <t>-21,19; -3,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,67; -1,95</t>
+          <t>-19,81; -2,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 9,0</t>
+          <t>-10,02; 6,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,29; -3,58</t>
+          <t>-14,16; -1,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -2,51</t>
+          <t>-15,86; -1,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 4,03</t>
+          <t>-9,27; 3,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -3,77</t>
+          <t>-15,17; -3,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -3,51</t>
+          <t>-14,61; -3,67</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-31,51%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-90,99%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-32,96%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-31,51%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-30,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-90,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-30,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-93,02%</t>
+          <t>-93,9%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,5; 168,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-83,16; 271,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,52; 93,09</t>
+          <t>-80,66; 86,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -49,59</t>
+          <t>-100,0; -49,08</t>
         </is>
       </c>
     </row>
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-4,01</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,61</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-11,07</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,18</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,62</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>-1,43</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,3</t>
+          <t>-3,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 5,91</t>
+          <t>-4,84; 7,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 4,69</t>
+          <t>-3,4; 8,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -4,55</t>
+          <t>-2,64; 15,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 6,71</t>
+          <t>-14,49; 6,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 8,1</t>
+          <t>-15,29; 4,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 15,8</t>
+          <t>-20,81; -3,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 4,71</t>
+          <t>-7,78; 4,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 4,52</t>
+          <t>-7,43; 4,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 3,14</t>
+          <t>-9,23; 3,37</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>58,02%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>109,09%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>205,35%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-36,24%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-41,63%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>58,02%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>109,09%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>181,22%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>-21,82%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-50,41%</t>
+          <t>-49,27%</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-85,61; 109,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,16; 187,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,11; 123,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-79,44; 149,63</t>
+          <t>-76,84; 142,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,15; 166,56</t>
+          <t>-70,8; 151,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-96,68; 179,64</t>
+          <t>-94,28; 199,01</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,42</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,26</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-7,09</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-7,09</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,06</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,42</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>-3,37</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>0,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 0,0</t>
+          <t>0,0; 12,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 5,66</t>
+          <t>1,44; 14,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,0</t>
+          <t>-20,74; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-23,29; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 16,02</t>
+          <t>-17,64; 6,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 1,27</t>
+          <t>-10,01; 1,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 0,0</t>
+          <t>-12,86; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 6,96</t>
+          <t>-7,59; 5,99</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-43,09%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>-47,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>8,72</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2,09</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5,52</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,25</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>3,34</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>8,72</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>-2,99</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,3</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 9,61</t>
+          <t>2,26; 20,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 14,67</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 4,9</t>
+          <t>0,0; 18,44</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,19; 20,22</t>
+          <t>-10,54; 8,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>-6,85; 14,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,35</t>
+          <t>-13,44; 2,33</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 11,0</t>
+          <t>-0,88; 10,91</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 8,72</t>
+          <t>-2,26; 9,48</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 7,95</t>
+          <t>-3,77; 7,53</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>4,74%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>63,36%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-53,04%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>-56,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-62,25; —</t>
+          <t>-59,59; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-6,14</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-2,34</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-3,41</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,06</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,65</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-5,13</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-6,14</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-2,34</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-3,77</t>
+          <t>-5,14</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-4,27</t>
+          <t>-4,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 8,99</t>
+          <t>-12,27; 0,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 4,66</t>
+          <t>-9,62; 6,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 0,56</t>
+          <t>-10,53; 10,18</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 0,05</t>
+          <t>-8,4; 7,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 5,41</t>
+          <t>-10,21; 4,43</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 8,07</t>
+          <t>-12,13; 1,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,34</t>
+          <t>-8,11; 1,94</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 2,53</t>
+          <t>-7,83; 2,63</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 3,66</t>
+          <t>-8,87; 3,41</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-66,91%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-25,54%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-37,18%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-31,99%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-61,91%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-66,91%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-25,54%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-41,09%</t>
+          <t>-62,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-48,89%</t>
+          <t>-46,79%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-68,56; 196,95</t>
+          <t>-93,45; 17,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-84,83; 137,76</t>
+          <t>-74,19; 131,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-92,36; 45,36</t>
+          <t>-92,18; 336,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-93,99; 57,91</t>
+          <t>-73,52; 174,25</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-76,34; 104,96</t>
+          <t>-85,64; 126,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-93,04; 208,09</t>
+          <t>-91,56; 91,58</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 48,78</t>
+          <t>-71,72; 38,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-71,13; 44,54</t>
+          <t>-68,46; 45,61</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-83,79; 94,03</t>
+          <t>-84,39; 77,28</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-3,17</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-2,78</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-1,3</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-2,1</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,6</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-1,06</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,14</t>
+          <t>-4,04; 4,84</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -0,57</t>
+          <t>-7,98; -0,81</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,45</t>
+          <t>-7,72; -0,65</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,39</t>
+          <t>-4,29; 1,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -0,8</t>
+          <t>-5,48; -0,56</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -0,08</t>
+          <t>-2,9; 5,77</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,08</t>
+          <t>-3,3; 1,91</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -0,99</t>
+          <t>-5,14; -1,1</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,77</t>
+          <t>-3,42; 1,51</t>
         </is>
       </c>
     </row>
@@ -2242,47 +2242,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-4,34%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-87,78%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-61,7%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>45,2%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-4,34%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>39,3%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-28,79%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-81,94%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-28,79%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-35,36%</t>
+          <t>-40,65%</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 565,7</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-88,03; 214,92</t>
+          <t>-85,74; 159,58</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 202,68</t>
+          <t>-89,07; 201,63</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-2,19</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-1,5</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-1,89</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-3,5</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-2,45</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,95</t>
+          <t>-3,66; 1,32</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,79</t>
+          <t>-4,45; 0,21</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -1,18</t>
+          <t>-4,01; 1,75</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,4</t>
+          <t>-4,22; 1,29</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,02</t>
+          <t>-4,65; 0,75</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,69</t>
+          <t>-6,29; -1,44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,57</t>
+          <t>-2,95; 0,52</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,23</t>
+          <t>-3,69; -0,23</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,51</t>
+          <t>-3,99; -0,33</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-22,0%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-45,24%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-30,27%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-26,21%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-33,18%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-61,23%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-22,0%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-45,24%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-30,05%</t>
+          <t>-61,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-45,7%</t>
+          <t>-46,47%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 24,26</t>
+          <t>-58,29; 41,08</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-62,76; 18,43</t>
+          <t>-72,3; 10,55</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-81,15; -26,09</t>
+          <t>-65,87; 53,28</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 46,11</t>
+          <t>-58,01; 31,32</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 2,91</t>
+          <t>-63,25; 19,33</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 53,05</t>
+          <t>-82,04; -29,11</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 13,74</t>
+          <t>-48,09; 13,32</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-60,15; -3,77</t>
+          <t>-59,72; -4,41</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-68,31; -6,83</t>
+          <t>-65,62; -5,19</t>
         </is>
       </c>
     </row>
